--- a/results/log_pv_cap/log_pv_cap_baseline_effects.xlsx
+++ b/results/log_pv_cap/log_pv_cap_baseline_effects.xlsx
@@ -511,291 +511,291 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.111</t>
+          <t>7.265</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.517</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.628</t>
+          <t>7.313</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.520</t>
+          <t>5.310</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.075</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.595</t>
+          <t>4.915</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.339</t>
+          <t>5.070</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.090</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.249</t>
+          <t>4.501</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-2.030</t>
+          <t>1.747</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.382</t>
+          <t>1.057</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-1.648</t>
+          <t>0.690</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>4.129</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.055</t>
+          <t>3.797</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3.466</t>
+          <t>4.318</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>4.184</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.134</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.509</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.265</t>
+          <t>-0.352</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.828</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.021</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.411</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.270</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.935</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.028</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.056</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.258</t>
+          <t>-0.284</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.153</t>
+          <t>-0.195</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.115</t>
+          <t>-0.141</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>-0.055</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.226</t>
+          <t>-0.254</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.059</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.207</t>
+          <t>-0.194</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.083</t>
+          <t>-0.119</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.072</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.068</t>
+          <t>-0.047</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.111</t>
+          <t>-0.129</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.119</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.096</t>
+          <t>-0.127</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.078</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.004</t>
         </is>
       </c>
     </row>
